--- a/InputData/fuels/PoFDCtAE/Perc of Fuel Demand Changes that Affect Exports.xlsx
+++ b/InputData/fuels/PoFDCtAE/Perc of Fuel Demand Changes that Affect Exports.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-us\InputData\fuels\PoFDCtAE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\fuels\PoFDCtAE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39172FEF-DF46-4438-98F5-4879A2699F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9377F1B-9CDE-4D4D-B017-2D898EEC5941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="-5760" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data from BFPIaE" sheetId="3" r:id="rId2"/>
-    <sheet name="PoFDCtAE" sheetId="2" r:id="rId3"/>
+    <sheet name="India data" sheetId="3" r:id="rId2"/>
+    <sheet name="Data from BFPIaE" sheetId="4" r:id="rId3"/>
+    <sheet name="PoFDCtAE" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,48 +39,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="123">
   <si>
     <t>PoFDCtAE Percentage of Fuel Demand Change that Alters Exports</t>
   </si>
   <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>U.S. Energy Information Administration</t>
-  </si>
-  <si>
-    <t>National Energy Modeling System Documentation</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/nems/documentation/international/pdf/m071(2018).pdf</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/nems/documentation/ngmm/pdf/ngmm(2018).pdf</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/nems/documentation/coal/pdf/m060(2018).pdf</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/outlooks/aeo/nems/documentation/ogsm/pdf/m063(2018).pdf</t>
+    <t>Source1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India Brand Equity Foundation </t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>Petroleum Planning and Analysis Cell</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Industry in India</t>
+  </si>
+  <si>
+    <t>Snapshot of India's Oil and Gas data</t>
+  </si>
+  <si>
+    <t>Snapshot - Government Initiatives</t>
+  </si>
+  <si>
+    <t>Self sufficiency in Petroleum Products</t>
+  </si>
+  <si>
+    <t>https://www.ibef.org/industry/oil-gas-india.aspx</t>
+  </si>
+  <si>
+    <t>https://ppac.gov.in/uploads/rep_studies/1670472940_202202040453534545669SnapshotofIndiaOilandGasdataDecember2021webupload.pdf</t>
+  </si>
+  <si>
+    <t>Tables 1.1 (Page 2), Table 2.6 (Page 9)</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>Notes - India</t>
+  </si>
+  <si>
     <t>Policy-driven changes in domestic fuel demand must be</t>
   </si>
   <si>
+    <t>In India's case, trends in the past decade show that domestic demand is largely</t>
+  </si>
+  <si>
     <t>apportioned to some combination of:</t>
   </si>
   <si>
+    <t xml:space="preserve">met through production and imports. The import dependency in nat gas </t>
+  </si>
+  <si>
+    <t>changes in domestic fuel production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and petroleum sectors has been high at 40-50% and 80-85% repectively </t>
+  </si>
+  <si>
     <t>changes in fuel imports</t>
   </si>
   <si>
+    <t xml:space="preserve">during 2015-19 (source 2). There are no exports in crude oil and natural </t>
+  </si>
+  <si>
     <t>changes in fuel exports</t>
   </si>
   <si>
-    <t>changes in domestic fuel production</t>
+    <t xml:space="preserve">gas. While India's petroleum refinery industry exports processed products, </t>
+  </si>
+  <si>
+    <t>in the overall basket of petroleum products there is a low percentage of self-sufficiency.</t>
   </si>
   <si>
     <t>Depending on the fuel or country, it can be desirable for changes</t>
@@ -85,27 +122,81 @@
     <t>in domestic demand to directly come out of exports (for example,</t>
   </si>
   <si>
+    <t>Further, there have been ongoing-policies to support indigenous exploration and</t>
+  </si>
+  <si>
     <t>an increase in oil use by a major oil exporting country already producing oil</t>
   </si>
   <si>
+    <t>production activities (e.g. 100% FDI in upstream and private sector refining projects)(source1)</t>
+  </si>
+  <si>
+    <t>at capacity would likely come out of its exports).  Alternatively, it can</t>
+  </si>
+  <si>
+    <t>Hence, the BAU impetus in the short- to medium term is on increasing production and</t>
+  </si>
+  <si>
     <t>be desirable for changes in demand to come out of production and</t>
   </si>
   <si>
-    <t>at capacity would likely come out of its exports).  Alternatively, it can</t>
+    <t xml:space="preserve">meeting domestic demand, along with increasing revenues from exports which </t>
   </si>
   <si>
     <t>imports (for example, if foreign demand for an exported fuel</t>
   </si>
   <si>
+    <t xml:space="preserve">are still not significant. </t>
+  </si>
+  <si>
     <t>is unaffected by domestic demand, and it is easy to ramp up or down</t>
   </si>
   <si>
+    <t xml:space="preserve">Hence, we assume that most of the domestic demand would be met by production </t>
+  </si>
+  <si>
     <t>production of that fuel to match changes in domestic demand).</t>
   </si>
   <si>
+    <t>and imports in the medium-term.</t>
+  </si>
+  <si>
     <t>This variable allows you to specify this behavior for a given country.</t>
   </si>
   <si>
+    <t>Data and sources from BFPIaE input file in 'Fuels' are applicable</t>
+  </si>
+  <si>
+    <t>The following examples may help you set this variable wisely:</t>
+  </si>
+  <si>
+    <t>Example 1: The United States</t>
+  </si>
+  <si>
+    <t>The United States is a major exporter of oil.  The U.S. has</t>
+  </si>
+  <si>
+    <t>a great deal of capacity to increase or decrease its own production</t>
+  </si>
+  <si>
+    <t>to meet demand.  Its oil is not exceptionally cheap to produce and</t>
+  </si>
+  <si>
+    <t>comes in around the global marginal price, accounting for shipping costs.</t>
+  </si>
+  <si>
+    <t>If the U.S. could export more oil profitably, it would already be doing so.</t>
+  </si>
+  <si>
+    <t>Changes in domestic oil demand are likely to be met with changes</t>
+  </si>
+  <si>
+    <t>in production and imports.</t>
+  </si>
+  <si>
+    <t>Example 2: Saudi Arabia</t>
+  </si>
+  <si>
     <t>Saudi Arabia is a major crude oil exporter.  Saudi Arabia's cost to produce</t>
   </si>
   <si>
@@ -133,208 +224,190 @@
     <t>rather than changes in production or imports.</t>
   </si>
   <si>
+    <t>Handling Crude Oil Export Changes due to Changes in Secondary Fuel Demand</t>
+  </si>
+  <si>
+    <t>A reduction in demand for a fuel derived from crude oil may result in</t>
+  </si>
+  <si>
+    <t>increased exports of that secondary fuel, or it may result in increased exports</t>
+  </si>
+  <si>
+    <t>of crude oil.  (Also, some of the demand reduction may cause reduced production</t>
+  </si>
+  <si>
+    <t>of both the secondary fuel and crude oil.)  To divide up these effects,</t>
+  </si>
+  <si>
+    <t>you may apportion the change in exports between that fuel and crude oil</t>
+  </si>
+  <si>
+    <t>along the same row.</t>
+  </si>
+  <si>
+    <t>For example, if demand for petroleum gasoline is reduced,</t>
+  </si>
+  <si>
+    <t>perhaps 25% of the amount by which the demand is reduced results in increased</t>
+  </si>
+  <si>
+    <t>exports of petroleum gasoline, 50% of the amount results in increased exports</t>
+  </si>
+  <si>
+    <t>of cruide oil, and 25% results in reduced production of both fuels.  You would</t>
+  </si>
+  <si>
+    <t>enter 0.25 in the (petroleum gasoline to petroleum gasoline) cell and 0.5 in the</t>
+  </si>
+  <si>
+    <t>(petroleum gasoline to crude oil) cell.</t>
+  </si>
+  <si>
+    <t>The total of each row may add to less than one (if some of the demand reduction</t>
+  </si>
+  <si>
+    <t>results in reduced production of both fuels), but no row may add to more</t>
+  </si>
+  <si>
+    <t>than one.</t>
+  </si>
+  <si>
+    <t>For an example of how to calculate the input data for this variable in</t>
+  </si>
+  <si>
+    <t>a region with non-zero changes in exports in response to chagnes in production,</t>
+  </si>
+  <si>
+    <t>see this variable in the Saudi Arabia version of the Energy Policy Simulator:</t>
+  </si>
+  <si>
+    <t>https://saudiarabia.energypolicy.solutions</t>
+  </si>
+  <si>
+    <t>Source: Snapshot of India's Oil and Gas data, 2021 (PPAC)</t>
+  </si>
+  <si>
+    <t>Table 7, Page 10</t>
+  </si>
+  <si>
+    <t>Table 2, Page 6</t>
+  </si>
+  <si>
+    <t>Start Year Data</t>
+  </si>
+  <si>
+    <t>Converted to BTU</t>
+  </si>
+  <si>
+    <t>Reasoning</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Imports</t>
+  </si>
+  <si>
+    <t>Exports</t>
+  </si>
+  <si>
+    <t>Domestic Use</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>We estimate the response to a drop in domestic use of a secondary petroleum product by observing how large</t>
+  </si>
+  <si>
     <t>electricity (not used in this variable)</t>
   </si>
   <si>
+    <t>the export market for that fuel is, versus the domestic use market.  If the fuel's exports are a far larger share</t>
+  </si>
+  <si>
     <t>hard coal</t>
   </si>
   <si>
+    <t>BTU</t>
+  </si>
+  <si>
+    <t>of the total outflows (exports + use) than use is, we assume the export market for that fuel can more easily</t>
+  </si>
+  <si>
     <t>natural gas</t>
   </si>
   <si>
+    <t>absorb the drop in domestic production.  Where a fuel is more commonly produced for domestic use (where</t>
+  </si>
+  <si>
+    <t>uranium</t>
+  </si>
+  <si>
+    <t>use has a larger share than exports of the total outflows), we assume less of that fuel will be produced, and</t>
+  </si>
+  <si>
+    <t>hydro (is not a fuel)</t>
+  </si>
+  <si>
+    <t>more crude will be exported instead.</t>
+  </si>
+  <si>
+    <t>wind (is not a fuel)</t>
+  </si>
+  <si>
+    <t>solar (is not a fuel)</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>petroleum gasoline</t>
+  </si>
+  <si>
+    <t>petroleum diesel</t>
+  </si>
+  <si>
+    <t>biofuel gasoline</t>
+  </si>
+  <si>
+    <t>biofuel diesel</t>
+  </si>
+  <si>
+    <t>jet fuel or kerosene</t>
+  </si>
+  <si>
+    <t>heat (not used in this variable)</t>
+  </si>
+  <si>
+    <t>geothermal (is not a fuel)</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy fuel oil</t>
+  </si>
+  <si>
+    <t>LPG propane or butane</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>Percentage Change in Demand that Alters Exports (dimensionless) - From type (below)  / To type (right)</t>
+  </si>
+  <si>
     <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro (is not a fuel)</t>
-  </si>
-  <si>
-    <t>wind (is not a fuel)</t>
-  </si>
-  <si>
-    <t>solar (is not a fuel)</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>petroleum gasoline</t>
-  </si>
-  <si>
-    <t>petroleum diesel</t>
-  </si>
-  <si>
-    <t>biofuel gasoline</t>
-  </si>
-  <si>
-    <t>biofuel diesel</t>
-  </si>
-  <si>
-    <t>jet fuel or kerosene</t>
-  </si>
-  <si>
-    <t>heat (not used in this variable)</t>
-  </si>
-  <si>
-    <t>geothermal (is not a fuel)</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy fuel oil</t>
-  </si>
-  <si>
-    <t>LPG propane or butane</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>Handling Crude Oil Export Changes due to Changes in Secondary Fuel Demand</t>
-  </si>
-  <si>
-    <t>A reduction in demand for a fuel derived from crude oil may result in</t>
-  </si>
-  <si>
-    <t>increased exports of that secondary fuel, or it may result in increased exports</t>
-  </si>
-  <si>
-    <t>of crude oil.  (Also, some of the demand reduction may cause reduced production</t>
-  </si>
-  <si>
-    <t>of both the secondary fuel and crude oil.)  To divide up these effects,</t>
-  </si>
-  <si>
-    <t>you may apportion the change in exports between that fuel and crude oil</t>
-  </si>
-  <si>
-    <t>along the same row.</t>
-  </si>
-  <si>
-    <t>The total of each row may add to less than one (if some of the demand reduction</t>
-  </si>
-  <si>
-    <t>results in reduced production of both fuels), but no row may add to more</t>
-  </si>
-  <si>
-    <t>than one.</t>
-  </si>
-  <si>
-    <t>perhaps 25% of the amount by which the demand is reduced results in increased</t>
-  </si>
-  <si>
-    <t>exports of petroleum gasoline, 50% of the amount results in increased exports</t>
-  </si>
-  <si>
-    <t>of cruide oil, and 25% results in reduced production of both fuels.  You would</t>
-  </si>
-  <si>
-    <t>enter 0.25 in the (petroleum gasoline to petroleum gasoline) cell and 0.5 in the</t>
-  </si>
-  <si>
-    <t>(petroleum gasoline to crude oil) cell.</t>
-  </si>
-  <si>
-    <t>For example, if demand for petroleum gasoline is reduced,</t>
-  </si>
-  <si>
-    <t>Percentage Change in Demand that Alters Exports (dimensionless) - From type (below)  / To type (right)</t>
-  </si>
-  <si>
-    <t>Converted to BTU</t>
-  </si>
-  <si>
-    <t>Fuel</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>Imports</t>
-  </si>
-  <si>
-    <t>Exports</t>
-  </si>
-  <si>
-    <t>Domestic Use</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>BTU</t>
-  </si>
-  <si>
-    <t>uranium</t>
-  </si>
-  <si>
-    <t>Start Year Data</t>
-  </si>
-  <si>
-    <t>Overall Approach and Assumptions</t>
-  </si>
-  <si>
-    <t>Apportioning Secondary Product Changes to That Product vs. Crude Oil</t>
-  </si>
-  <si>
-    <t>see variable fuels/BFPIaE</t>
-  </si>
-  <si>
-    <t>We estimate the response to a drop in domestic use of a secondary petroleum product by observing how large</t>
-  </si>
-  <si>
-    <t>the export market for that fuel is, versus the domestic use market.  If the fuel's exports are a far larger share</t>
-  </si>
-  <si>
-    <t>of the total outflows (exports + use) than use is, we assume the export market for that fuel can more easily</t>
-  </si>
-  <si>
-    <t>absorb the drop in domestic production.  Where a fuel is more commonly produced for domestic use (where</t>
-  </si>
-  <si>
-    <t>use has a larger share than exports of the total outflows), we assume less of that fuel will be produced, and</t>
-  </si>
-  <si>
-    <t>more crude will be exported instead.</t>
-  </si>
-  <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>The following example may help you set this variable wisely:</t>
-  </si>
-  <si>
-    <t>Example 1: Saudi Arabia</t>
-  </si>
-  <si>
-    <t>United States Settings</t>
-  </si>
-  <si>
-    <t>Based on consultation with oil market experts at Rapidian Energy and Wood Mackenzie,</t>
-  </si>
-  <si>
-    <t>in a high electrification scenario), and the difference would be made up by increased exports,</t>
-  </si>
-  <si>
-    <t>similar to the Saudi Arabia example above.</t>
-  </si>
-  <si>
-    <t>day exports / present day production), which should roughly express how important the export market</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> for that fuel for U.S. producers.</t>
-  </si>
-  <si>
-    <t>we believe U.S. oil production would be relatively unaffected by a drop in U.S. demand (for instance,</t>
-  </si>
-  <si>
-    <t>For fuels other than crude oil and petroleum products, we use settings calculated as (present</t>
   </si>
 </sst>
 </file>
@@ -344,7 +417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +449,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -398,7 +485,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +503,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -457,20 +544,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -490,17 +580,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -517,6 +605,98 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>97733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4B36B0A-70C8-8720-CD9A-55DEA135EB2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect r="2022" b="3531"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25400" y="281883"/>
+          <a:ext cx="7016750" cy="3020118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>332855</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>69000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C0F4CC-1189-945A-ABB5-3BF1CFDC9BDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31750" y="4203700"/>
+          <a:ext cx="7616305" cy="5072800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -782,766 +962,908 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="87.54296875" customWidth="1"/>
+    <col min="2" max="2" width="58.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="64.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
+        <v>2019</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="11"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="14"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="14"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="14"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="2">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B13" s="25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="26"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>62</v>
-      </c>
+      <c r="B73" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A73" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A20:A54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.1796875" customWidth="1"/>
-    <col min="2" max="5" width="15.453125" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="100.7265625" customWidth="1"/>
+    <col min="1" max="1" width="44.140625" customWidth="1"/>
+    <col min="2" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="100.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
-      <c r="H2" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="H2" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>76</v>
+      <c r="D3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>92</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
+        <v>94</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="26"/>
       <c r="H4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="22">
-        <v>1.3864106347E+16</v>
-      </c>
-      <c r="C5" s="22">
-        <v>117950568000000</v>
-      </c>
-      <c r="D5" s="22">
-        <v>1906867516000000</v>
-      </c>
-      <c r="E5" s="22">
-        <v>1.2075189399E+16</v>
+        <v>96</v>
+      </c>
+      <c r="B5" s="30">
+        <v>1.116E+16</v>
+      </c>
+      <c r="C5" s="27">
+        <v>2991850000000000</v>
+      </c>
+      <c r="D5" s="27">
+        <v>16678200000000</v>
+      </c>
+      <c r="E5" s="25">
+        <f t="shared" ref="E5:E24" si="0">B5+C5-D5</f>
+        <v>1.41351718E+16</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="22">
-        <v>3.5682777E+16</v>
-      </c>
-      <c r="C6" s="22">
-        <v>2798295000000000</v>
-      </c>
-      <c r="D6" s="22">
-        <v>6809672000000000</v>
-      </c>
-      <c r="E6" s="22">
-        <v>3.1671400000000004E+16</v>
+        <v>99</v>
+      </c>
+      <c r="B6" s="30">
+        <v>1224860000000000</v>
+      </c>
+      <c r="C6" s="27">
+        <v>1117010000000000</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25">
+        <f t="shared" si="0"/>
+        <v>2341870000000000</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="22">
-        <v>540000000000000</v>
-      </c>
-      <c r="C7" s="22">
-        <v>7200000000000000</v>
-      </c>
-      <c r="D7" s="22">
-        <v>0</v>
-      </c>
-      <c r="E7" s="22">
-        <v>7740000000000000</v>
+        <v>101</v>
+      </c>
+      <c r="B7" s="30">
+        <v>140503000000000</v>
+      </c>
+      <c r="C7" s="27">
+        <v>228298000000000</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="25">
+        <f t="shared" si="0"/>
+        <v>368801000000000</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
+        <v>103</v>
+      </c>
+      <c r="B8" s="31">
+        <v>0</v>
+      </c>
+      <c r="C8" s="31">
+        <v>0</v>
+      </c>
+      <c r="D8" s="31">
+        <v>0</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
       <c r="H8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+      <c r="B9" s="31">
+        <v>0</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="B10" s="31">
+        <v>0</v>
+      </c>
+      <c r="C10" s="31">
+        <v>0</v>
+      </c>
+      <c r="D10" s="31">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="22">
-        <v>166043036334000</v>
-      </c>
-      <c r="C11" s="22">
-        <v>5522103312930.1787</v>
-      </c>
-      <c r="D11" s="22">
-        <v>124444981024000</v>
-      </c>
-      <c r="E11" s="20">
-        <v>47120158622930.172</v>
+        <v>107</v>
+      </c>
+      <c r="B11" s="30">
+        <v>3010000000000000</v>
+      </c>
+      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25">
+        <f t="shared" si="0"/>
+        <v>3010000000000000</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="22">
-        <v>1.8360236509349E+16</v>
-      </c>
-      <c r="C12" s="22">
-        <v>59529362424000</v>
-      </c>
-      <c r="D12" s="22">
-        <v>1381557079413000</v>
-      </c>
-      <c r="E12" s="20">
-        <v>1.703820879236E+16</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="30">
+        <v>1780000000000000</v>
+      </c>
+      <c r="C12" s="27">
+        <v>29600000000000</v>
+      </c>
+      <c r="D12" s="27">
+        <v>595000000000000</v>
+      </c>
+      <c r="E12" s="25">
+        <f t="shared" si="0"/>
+        <v>1214600000000000</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="22">
-        <v>1.0682345175E+16</v>
-      </c>
-      <c r="C13" s="22">
-        <v>320229375000000</v>
-      </c>
-      <c r="D13" s="22">
-        <v>2936702875000000</v>
-      </c>
-      <c r="E13" s="20">
-        <v>8065871675000000</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="30">
+        <v>4740000000000000</v>
+      </c>
+      <c r="C13" s="27">
+        <v>3320000000000</v>
+      </c>
+      <c r="D13" s="27">
+        <v>1430000000000000</v>
+      </c>
+      <c r="E13" s="25">
+        <f t="shared" si="0"/>
+        <v>3313320000000000</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="22">
-        <v>1515620096655000</v>
-      </c>
-      <c r="C14" s="22">
-        <v>7285809312000</v>
-      </c>
-      <c r="D14" s="22">
-        <v>132183114996000</v>
-      </c>
-      <c r="E14" s="20">
-        <v>1390722790971000</v>
+        <v>110</v>
+      </c>
+      <c r="B14" s="30">
+        <v>71035200000000</v>
+      </c>
+      <c r="C14" s="27">
+        <v>0</v>
+      </c>
+      <c r="D14" s="27">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25">
+        <f t="shared" si="0"/>
+        <v>71035200000000</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="22">
-        <v>203604487000000</v>
-      </c>
-      <c r="C15" s="22">
-        <v>74398997000000</v>
-      </c>
-      <c r="D15" s="22">
-        <v>11939852000000</v>
-      </c>
-      <c r="E15" s="20">
-        <v>266063632000000</v>
+        <v>111</v>
+      </c>
+      <c r="B15" s="30">
+        <v>17758800000000</v>
+      </c>
+      <c r="C15" s="27">
+        <v>0</v>
+      </c>
+      <c r="D15" s="27">
+        <v>0</v>
+      </c>
+      <c r="E15" s="25">
+        <f t="shared" si="0"/>
+        <v>17758800000000</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="22">
-        <v>3537592380000000</v>
-      </c>
-      <c r="C16" s="22">
-        <v>338510340000000</v>
-      </c>
-      <c r="D16" s="22">
-        <v>393656760000000</v>
-      </c>
-      <c r="E16" s="20">
-        <v>3482445960000000</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="30">
+        <v>472847000000000</v>
+      </c>
+      <c r="C16" s="27">
+        <v>5635980000000</v>
+      </c>
+      <c r="D16" s="27">
+        <v>0</v>
+      </c>
+      <c r="E16" s="32">
+        <f>B16+C16-D16</f>
+        <v>478482980000000</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="B17" s="31">
+        <v>0</v>
+      </c>
+      <c r="C17" s="31">
+        <v>0</v>
+      </c>
+      <c r="D17" s="31">
+        <v>0</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="B18" s="31">
+        <v>0</v>
+      </c>
+      <c r="C18" s="31">
+        <v>0</v>
+      </c>
+      <c r="D18" s="31">
+        <v>0</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="22">
-        <v>906213062527442.13</v>
-      </c>
-      <c r="C19" s="22">
-        <v>0</v>
-      </c>
-      <c r="D19" s="22">
-        <v>0</v>
-      </c>
-      <c r="E19" s="20">
-        <v>906213062527442.13</v>
+        <v>115</v>
+      </c>
+      <c r="B19" s="30">
+        <v>633227000000000</v>
+      </c>
+      <c r="C19" s="27">
+        <v>138667000000</v>
+      </c>
+      <c r="D19" s="27">
+        <v>58666666667</v>
+      </c>
+      <c r="E19" s="25">
+        <f t="shared" si="0"/>
+        <v>633307000333333</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="22">
-        <v>2.3255085897106E+16</v>
-      </c>
-      <c r="C20" s="22">
-        <v>1.269962477E+16</v>
-      </c>
-      <c r="D20" s="22">
-        <v>6193988558562000</v>
-      </c>
-      <c r="E20" s="20">
-        <v>2.9760722108544E+16</v>
+        <v>116</v>
+      </c>
+      <c r="B20" s="30">
+        <v>1244820000000000</v>
+      </c>
+      <c r="C20" s="27">
+        <v>9532210000000000</v>
+      </c>
+      <c r="D20" s="27">
+        <v>0</v>
+      </c>
+      <c r="E20" s="25">
+        <f t="shared" si="0"/>
+        <v>1.077703E+16</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="22">
-        <v>979835237000000</v>
-      </c>
-      <c r="C21" s="22">
-        <v>433897305000000</v>
-      </c>
-      <c r="D21" s="22">
-        <v>705652880000000</v>
-      </c>
-      <c r="E21" s="20">
-        <v>708079662000000</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="30">
+        <v>352851000000000</v>
+      </c>
+      <c r="C21" s="27">
+        <v>72714400000000</v>
+      </c>
+      <c r="D21" s="27">
+        <v>105597000000000</v>
+      </c>
+      <c r="E21" s="25">
+        <f t="shared" si="0"/>
+        <v>319968400000000</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="22">
-        <v>4171558240080000</v>
-      </c>
-      <c r="C22" s="22">
-        <v>219065893200000</v>
-      </c>
-      <c r="D22" s="22">
-        <v>2412911377800000</v>
-      </c>
-      <c r="E22" s="20">
-        <v>1977712755480000</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="30">
+        <v>548000000000000</v>
+      </c>
+      <c r="C22" s="27">
+        <v>767000000000000</v>
+      </c>
+      <c r="D22" s="27">
+        <v>23000000000000</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="0"/>
+        <v>1292000000000000</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="22">
-        <v>3564295858911020.5</v>
-      </c>
-      <c r="C23" s="22">
-        <v>0</v>
-      </c>
-      <c r="D23" s="22">
-        <v>0</v>
-      </c>
-      <c r="E23" s="20">
-        <v>3564295858911020.5</v>
+        <v>119</v>
+      </c>
+      <c r="B23" s="30">
+        <v>292326000000000</v>
+      </c>
+      <c r="C23" s="27">
+        <v>0</v>
+      </c>
+      <c r="D23" s="27">
+        <v>0</v>
+      </c>
+      <c r="E23" s="25">
+        <f t="shared" si="0"/>
+        <v>292326000000000</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="22">
-        <v>8746500000000000</v>
-      </c>
-      <c r="C24" s="22">
-        <v>0</v>
-      </c>
-      <c r="D24" s="22">
-        <v>0</v>
-      </c>
-      <c r="E24" s="20">
-        <v>8746500000000000</v>
+        <v>120</v>
+      </c>
+      <c r="B24" s="31">
+        <v>0</v>
+      </c>
+      <c r="C24" s="31">
+        <v>0</v>
+      </c>
+      <c r="D24" s="31">
+        <v>0</v>
+      </c>
+      <c r="E24" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1549,89 +1871,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7265625" customWidth="1"/>
-    <col min="2" max="22" width="16.54296875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="22" width="16.5703125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -1697,16 +2019,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="B3" s="5">
         <v>0</v>
       </c>
-      <c r="C3" s="28">
-        <f>'Data from BFPIaE'!D5/'Data from BFPIaE'!B5</f>
-        <v>0.13753987947536334</v>
+      <c r="C3" s="7">
+        <v>0</v>
       </c>
       <c r="D3" s="7">
         <v>0</v>
@@ -1766,9 +2087,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="B4" s="5">
         <v>0</v>
@@ -1776,9 +2097,8 @@
       <c r="C4" s="7">
         <v>0</v>
       </c>
-      <c r="D4" s="28">
-        <f>'Data from BFPIaE'!D6/'Data from BFPIaE'!B6</f>
-        <v>0.19083918272392308</v>
+      <c r="D4" s="7">
+        <v>0</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -1835,9 +2155,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -1848,8 +2168,7 @@
       <c r="D5" s="7">
         <v>0</v>
       </c>
-      <c r="E5" s="28">
-        <f>'Data from BFPIaE'!D7/'Data from BFPIaE'!B7</f>
+      <c r="E5" s="7">
         <v>0</v>
       </c>
       <c r="F5" s="5">
@@ -1904,9 +2223,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
@@ -1972,9 +2291,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -2040,9 +2359,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="B8" s="5">
         <v>0</v>
@@ -2108,9 +2427,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="B9" s="5">
         <v>0</v>
@@ -2133,9 +2452,8 @@
       <c r="H9" s="5">
         <v>0</v>
       </c>
-      <c r="I9" s="28">
-        <f>'Data from BFPIaE'!D11/'Data from BFPIaE'!B11</f>
-        <v>0.74947425541939383</v>
+      <c r="I9" s="7">
+        <v>0</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -2177,9 +2495,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
@@ -2205,9 +2523,9 @@
       <c r="I10" s="7">
         <v>0</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="29">
         <f>'Data from BFPIaE'!D12/SUM('Data from BFPIaE'!D12:E12)</f>
-        <v>7.5004052116109651E-2</v>
+        <v>0.32880194518125555</v>
       </c>
       <c r="K10" s="7">
         <v>0</v>
@@ -2230,9 +2548,8 @@
       <c r="Q10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="11">
-        <f>1-J10</f>
-        <v>0.92499594788389039</v>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
       <c r="S10" s="7">
         <v>0</v>
@@ -2247,9 +2564,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B11" s="5">
         <v>0</v>
@@ -2278,9 +2595,9 @@
       <c r="J11" s="7">
         <v>0</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="29">
         <f>'Data from BFPIaE'!D13/SUM('Data from BFPIaE'!D13:E13)</f>
-        <v>0.26691051822957201</v>
+        <v>0.30147660288574246</v>
       </c>
       <c r="L11" s="7">
         <v>0</v>
@@ -2300,9 +2617,8 @@
       <c r="Q11" s="7">
         <v>0</v>
       </c>
-      <c r="R11" s="11">
-        <f>1-K11</f>
-        <v>0.73308948177042799</v>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
       <c r="S11" s="7">
         <v>0</v>
@@ -2317,9 +2633,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5">
         <v>0</v>
@@ -2351,9 +2667,8 @@
       <c r="K12" s="7">
         <v>0</v>
       </c>
-      <c r="L12" s="28">
-        <f>'Data from BFPIaE'!D14/'Data from BFPIaE'!B14</f>
-        <v>8.7213883800914521E-2</v>
+      <c r="L12" s="7">
+        <v>0</v>
       </c>
       <c r="M12" s="7">
         <v>0</v>
@@ -2386,9 +2701,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="B13" s="5">
         <v>0</v>
@@ -2423,9 +2738,8 @@
       <c r="L13" s="7">
         <v>0</v>
       </c>
-      <c r="M13" s="28">
-        <f>'Data from BFPIaE'!D15/'Data from BFPIaE'!B15</f>
-        <v>5.8642381491327347E-2</v>
+      <c r="M13" s="7">
+        <v>0</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
@@ -2455,9 +2769,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="B14" s="5">
         <v>0</v>
@@ -2495,9 +2809,8 @@
       <c r="M14" s="7">
         <v>0</v>
       </c>
-      <c r="N14" s="10">
-        <f>'Data from BFPIaE'!D16/SUM('Data from BFPIaE'!D16:E16)</f>
-        <v>0.10155994008332163</v>
+      <c r="N14" s="7">
+        <v>0</v>
       </c>
       <c r="O14" s="5">
         <v>0</v>
@@ -2508,9 +2821,8 @@
       <c r="Q14" s="7">
         <v>0</v>
       </c>
-      <c r="R14" s="11">
-        <f>1-N14</f>
-        <v>0.89844005991667841</v>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
       <c r="S14" s="7">
         <v>0</v>
@@ -2525,9 +2837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B15" s="5">
         <v>0</v>
@@ -2593,9 +2905,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
@@ -2661,9 +2973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
@@ -2710,8 +3022,7 @@
       <c r="P17" s="5">
         <v>0</v>
       </c>
-      <c r="Q17" s="28">
-        <f>'Data from BFPIaE'!D19/'Data from BFPIaE'!B19</f>
+      <c r="Q17" s="7">
         <v>0</v>
       </c>
       <c r="R17" s="7">
@@ -2730,9 +3041,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5">
         <v>0</v>
@@ -2782,8 +3093,8 @@
       <c r="Q18" s="7">
         <v>0</v>
       </c>
-      <c r="R18" s="10">
-        <v>1</v>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
       <c r="S18" s="7">
         <v>0</v>
@@ -2798,9 +3109,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -2850,13 +3161,11 @@
       <c r="Q19" s="7">
         <v>0</v>
       </c>
-      <c r="R19" s="11">
-        <f>1-S19</f>
-        <v>0.50085828893652218</v>
-      </c>
-      <c r="S19" s="10">
-        <f>'Data from BFPIaE'!D21/SUM('Data from BFPIaE'!D21:E21)</f>
-        <v>0.49914171106347782</v>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0</v>
       </c>
       <c r="T19" s="7">
         <v>0</v>
@@ -2868,9 +3177,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="B20" s="5">
         <v>0</v>
@@ -2920,16 +3229,14 @@
       <c r="Q20" s="7">
         <v>0</v>
       </c>
-      <c r="R20" s="11">
-        <f>1-T20</f>
-        <v>0.45044000475680823</v>
+      <c r="R20" s="7">
+        <v>0</v>
       </c>
       <c r="S20" s="7">
         <v>0</v>
       </c>
-      <c r="T20" s="10">
-        <f>'Data from BFPIaE'!D22/SUM('Data from BFPIaE'!D22:E22)</f>
-        <v>0.54955999524319177</v>
+      <c r="T20" s="7">
+        <v>0</v>
       </c>
       <c r="U20" s="7">
         <v>0</v>
@@ -2938,9 +3245,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B21" s="5">
         <v>0</v>
@@ -2999,17 +3306,16 @@
       <c r="T21" s="7">
         <v>0</v>
       </c>
-      <c r="U21" s="28">
-        <f>'Data from BFPIaE'!D23/'Data from BFPIaE'!B23</f>
+      <c r="U21" s="7">
         <v>0</v>
       </c>
       <c r="V21" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="B22" s="5">
         <v>0</v>
@@ -3071,12 +3377,205 @@
       <c r="U22" s="7">
         <v>0</v>
       </c>
-      <c r="V22" s="28">
-        <f>'Data from BFPIaE'!D24/'Data from BFPIaE'!B24</f>
+      <c r="V22" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A89FCB-FFDB-4387-9B3F-9098F5DCBDC2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6795757E-8E33-41FD-9B05-B2FBEEE7C965}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F467A879-7FAA-44E5-B8CA-B56D9F10EBF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>